--- a/dataset_t6_grouped/results2/G4/G4_T3616_W0026F0002T0006Z000C1N102_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3616_W0026F0002T0006Z000C1N102_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>86.99460961419454</v>
+        <v>14.13662406230661</v>
       </c>
       <c r="D2" t="n">
-        <v>31.8059742815717</v>
+        <v>5.168470820755402</v>
       </c>
       <c r="E2" t="n">
-        <v>13.62289552379796</v>
+        <v>2.213720522617169</v>
       </c>
       <c r="F2" t="n">
-        <v>11.77564223685617</v>
+        <v>1.913541863489128</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>59.74881856659863</v>
+        <v>9.709183017072277</v>
       </c>
       <c r="D3" t="n">
-        <v>55.35725875528404</v>
+        <v>8.995554547733658</v>
       </c>
       <c r="E3" t="n">
-        <v>13.62289552379796</v>
+        <v>2.213720522617169</v>
       </c>
       <c r="F3" t="n">
-        <v>11.77564223685617</v>
+        <v>1.913541863489128</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
